--- a/DISASTER/erosion_site_intervention.xlsx
+++ b/DISASTER/erosion_site_intervention.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="21">
   <si>
     <t>id</t>
   </si>
@@ -25,7 +25,7 @@
     <t>year</t>
   </si>
   <si>
-    <t>erosion_site_id</t>
+    <t>erosion_site</t>
   </si>
   <si>
     <t>type_of_erosion</t>
@@ -35,6 +35,45 @@
   </si>
   <si>
     <t>avg_depth_in_metres</t>
+  </si>
+  <si>
+    <t>Amachalla, Awka</t>
+  </si>
+  <si>
+    <t>Federal High Court/Ekwueme Square, Awka (Palliative)</t>
+  </si>
+  <si>
+    <t>Neroz Plaza/ St Thomas Aquinas</t>
+  </si>
+  <si>
+    <t>Ugamuma-Obosi Obosi</t>
+  </si>
+  <si>
+    <t>Ire-Obosi</t>
+  </si>
+  <si>
+    <t>Nkpor-Flyover</t>
+  </si>
+  <si>
+    <t>Abidi-Umuoji</t>
+  </si>
+  <si>
+    <t>Ikenga-Ogidi</t>
+  </si>
+  <si>
+    <t>Ojoto</t>
+  </si>
+  <si>
+    <t>Abagana</t>
+  </si>
+  <si>
+    <t>Enugwu-Ukwu</t>
+  </si>
+  <si>
+    <t>Nnewichi</t>
+  </si>
+  <si>
+    <t>Omagba/New Heritage</t>
   </si>
   <si>
     <t>Gully</t>
@@ -431,11 +470,11 @@
       <c r="C2">
         <v>2019</v>
       </c>
-      <c r="D2">
-        <v>0</v>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -454,11 +493,11 @@
       <c r="C3">
         <v>2019</v>
       </c>
-      <c r="D3">
-        <v>1</v>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>3.49</v>
@@ -477,11 +516,11 @@
       <c r="C4">
         <v>2019</v>
       </c>
-      <c r="D4">
-        <v>2</v>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1.3</v>
@@ -500,11 +539,11 @@
       <c r="C5">
         <v>2019</v>
       </c>
-      <c r="D5">
-        <v>3</v>
+      <c r="D5" t="s">
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>10.88</v>
@@ -523,11 +562,11 @@
       <c r="C6">
         <v>2019</v>
       </c>
-      <c r="D6">
-        <v>4</v>
+      <c r="D6" t="s">
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>16.6</v>
@@ -546,11 +585,11 @@
       <c r="C7">
         <v>2019</v>
       </c>
-      <c r="D7">
-        <v>5</v>
+      <c r="D7" t="s">
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>5.4</v>
@@ -569,11 +608,11 @@
       <c r="C8">
         <v>2019</v>
       </c>
-      <c r="D8">
-        <v>6</v>
+      <c r="D8" t="s">
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>2.65</v>
@@ -592,11 +631,11 @@
       <c r="C9">
         <v>2019</v>
       </c>
-      <c r="D9">
-        <v>7</v>
+      <c r="D9" t="s">
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -615,11 +654,11 @@
       <c r="C10">
         <v>2019</v>
       </c>
-      <c r="D10">
-        <v>8</v>
+      <c r="D10" t="s">
+        <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>7.7</v>
@@ -638,11 +677,11 @@
       <c r="C11">
         <v>2019</v>
       </c>
-      <c r="D11">
-        <v>9</v>
+      <c r="D11" t="s">
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>4.8</v>
@@ -661,11 +700,11 @@
       <c r="C12">
         <v>2019</v>
       </c>
-      <c r="D12">
-        <v>10</v>
+      <c r="D12" t="s">
+        <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>2.33</v>
@@ -684,11 +723,11 @@
       <c r="C13">
         <v>2019</v>
       </c>
-      <c r="D13">
-        <v>11</v>
+      <c r="D13" t="s">
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>31.86</v>
@@ -707,11 +746,11 @@
       <c r="C14">
         <v>2019</v>
       </c>
-      <c r="D14">
-        <v>12</v>
+      <c r="D14" t="s">
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F14">
         <v>1.13</v>
@@ -730,11 +769,11 @@
       <c r="C15">
         <v>2020</v>
       </c>
-      <c r="D15">
-        <v>0</v>
+      <c r="D15" t="s">
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -753,11 +792,11 @@
       <c r="C16">
         <v>2020</v>
       </c>
-      <c r="D16">
-        <v>1</v>
+      <c r="D16" t="s">
+        <v>8</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -776,11 +815,11 @@
       <c r="C17">
         <v>2020</v>
       </c>
-      <c r="D17">
-        <v>2</v>
+      <c r="D17" t="s">
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -799,11 +838,11 @@
       <c r="C18">
         <v>2020</v>
       </c>
-      <c r="D18">
-        <v>3</v>
+      <c r="D18" t="s">
+        <v>10</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>9.9</v>
@@ -822,11 +861,11 @@
       <c r="C19">
         <v>2020</v>
       </c>
-      <c r="D19">
-        <v>4</v>
+      <c r="D19" t="s">
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F19">
         <v>6.3</v>
@@ -845,11 +884,11 @@
       <c r="C20">
         <v>2020</v>
       </c>
-      <c r="D20">
-        <v>5</v>
+      <c r="D20" t="s">
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F20">
         <v>3</v>
@@ -868,11 +907,11 @@
       <c r="C21">
         <v>2020</v>
       </c>
-      <c r="D21">
-        <v>6</v>
+      <c r="D21" t="s">
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F21">
         <v>1.8</v>
@@ -891,11 +930,11 @@
       <c r="C22">
         <v>2020</v>
       </c>
-      <c r="D22">
-        <v>7</v>
+      <c r="D22" t="s">
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F22">
         <v>2.36</v>
@@ -914,11 +953,11 @@
       <c r="C23">
         <v>2020</v>
       </c>
-      <c r="D23">
-        <v>8</v>
+      <c r="D23" t="s">
+        <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F23">
         <v>2.8</v>
@@ -937,11 +976,11 @@
       <c r="C24">
         <v>2020</v>
       </c>
-      <c r="D24">
-        <v>9</v>
+      <c r="D24" t="s">
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F24">
         <v>2.7</v>
@@ -960,11 +999,11 @@
       <c r="C25">
         <v>2020</v>
       </c>
-      <c r="D25">
-        <v>10</v>
+      <c r="D25" t="s">
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F25">
         <v>1.9</v>
@@ -983,11 +1022,11 @@
       <c r="C26">
         <v>2020</v>
       </c>
-      <c r="D26">
-        <v>11</v>
+      <c r="D26" t="s">
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F26">
         <v>9.800000000000001</v>
@@ -1006,11 +1045,11 @@
       <c r="C27">
         <v>2020</v>
       </c>
-      <c r="D27">
-        <v>12</v>
+      <c r="D27" t="s">
+        <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F27">
         <v>0.05</v>
@@ -1029,11 +1068,11 @@
       <c r="C28">
         <v>2021</v>
       </c>
-      <c r="D28">
-        <v>0</v>
+      <c r="D28" t="s">
+        <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -1052,11 +1091,11 @@
       <c r="C29">
         <v>2021</v>
       </c>
-      <c r="D29">
-        <v>1</v>
+      <c r="D29" t="s">
+        <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1075,11 +1114,11 @@
       <c r="C30">
         <v>2021</v>
       </c>
-      <c r="D30">
-        <v>2</v>
+      <c r="D30" t="s">
+        <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1098,11 +1137,11 @@
       <c r="C31">
         <v>2021</v>
       </c>
-      <c r="D31">
-        <v>3</v>
+      <c r="D31" t="s">
+        <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F31">
         <v>6.3</v>
@@ -1121,11 +1160,11 @@
       <c r="C32">
         <v>2021</v>
       </c>
-      <c r="D32">
-        <v>4</v>
+      <c r="D32" t="s">
+        <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F32">
         <v>7.5</v>
@@ -1144,11 +1183,11 @@
       <c r="C33">
         <v>2021</v>
       </c>
-      <c r="D33">
-        <v>5</v>
+      <c r="D33" t="s">
+        <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F33">
         <v>3.9</v>
@@ -1167,11 +1206,11 @@
       <c r="C34">
         <v>2021</v>
       </c>
-      <c r="D34">
-        <v>6</v>
+      <c r="D34" t="s">
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1190,11 +1229,11 @@
       <c r="C35">
         <v>2021</v>
       </c>
-      <c r="D35">
-        <v>7</v>
+      <c r="D35" t="s">
+        <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F35">
         <v>2.8</v>
@@ -1213,11 +1252,11 @@
       <c r="C36">
         <v>2021</v>
       </c>
-      <c r="D36">
-        <v>8</v>
+      <c r="D36" t="s">
+        <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1236,11 +1275,11 @@
       <c r="C37">
         <v>2021</v>
       </c>
-      <c r="D37">
-        <v>9</v>
+      <c r="D37" t="s">
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -1259,11 +1298,11 @@
       <c r="C38">
         <v>2021</v>
       </c>
-      <c r="D38">
-        <v>10</v>
+      <c r="D38" t="s">
+        <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F38">
         <v>0.5</v>
@@ -1282,11 +1321,11 @@
       <c r="C39">
         <v>2021</v>
       </c>
-      <c r="D39">
-        <v>11</v>
+      <c r="D39" t="s">
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F39">
         <v>3</v>
@@ -1305,11 +1344,11 @@
       <c r="C40">
         <v>2021</v>
       </c>
-      <c r="D40">
-        <v>12</v>
+      <c r="D40" t="s">
+        <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F40">
         <v>0.04</v>
@@ -1328,11 +1367,11 @@
       <c r="C41">
         <v>2022</v>
       </c>
-      <c r="D41">
-        <v>0</v>
+      <c r="D41" t="s">
+        <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1351,11 +1390,11 @@
       <c r="C42">
         <v>2022</v>
       </c>
-      <c r="D42">
-        <v>1</v>
+      <c r="D42" t="s">
+        <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1374,11 +1413,11 @@
       <c r="C43">
         <v>2022</v>
       </c>
-      <c r="D43">
-        <v>2</v>
+      <c r="D43" t="s">
+        <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1397,11 +1436,11 @@
       <c r="C44">
         <v>2022</v>
       </c>
-      <c r="D44">
-        <v>3</v>
+      <c r="D44" t="s">
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F44">
         <v>5.5</v>
@@ -1420,11 +1459,11 @@
       <c r="C45">
         <v>2022</v>
       </c>
-      <c r="D45">
-        <v>4</v>
+      <c r="D45" t="s">
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F45">
         <v>2</v>
@@ -1443,11 +1482,11 @@
       <c r="C46">
         <v>2022</v>
       </c>
-      <c r="D46">
-        <v>5</v>
+      <c r="D46" t="s">
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F46">
         <v>2.8</v>
@@ -1466,11 +1505,11 @@
       <c r="C47">
         <v>2022</v>
       </c>
-      <c r="D47">
-        <v>6</v>
+      <c r="D47" t="s">
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -1489,11 +1528,11 @@
       <c r="C48">
         <v>2022</v>
       </c>
-      <c r="D48">
-        <v>7</v>
+      <c r="D48" t="s">
+        <v>14</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F48">
         <v>2.5</v>
@@ -1512,11 +1551,11 @@
       <c r="C49">
         <v>2022</v>
       </c>
-      <c r="D49">
-        <v>8</v>
+      <c r="D49" t="s">
+        <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -1535,11 +1574,11 @@
       <c r="C50">
         <v>2022</v>
       </c>
-      <c r="D50">
-        <v>9</v>
+      <c r="D50" t="s">
+        <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F50">
         <v>1.5</v>
@@ -1558,11 +1597,11 @@
       <c r="C51">
         <v>2022</v>
       </c>
-      <c r="D51">
-        <v>10</v>
+      <c r="D51" t="s">
+        <v>17</v>
       </c>
       <c r="E51" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -1581,11 +1620,11 @@
       <c r="C52">
         <v>2022</v>
       </c>
-      <c r="D52">
-        <v>11</v>
+      <c r="D52" t="s">
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1604,11 +1643,11 @@
       <c r="C53">
         <v>2022</v>
       </c>
-      <c r="D53">
-        <v>12</v>
+      <c r="D53" t="s">
+        <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F53">
         <v>0</v>
